--- a/BVSimulationFiles/97.xlsx
+++ b/BVSimulationFiles/97.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.0003902439024390245</v>
+        <v>0.000780487804878049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0003963024778901831</v>
+        <v>0.0007926049557803662</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0004011307673154035</v>
+        <v>0.000802261534630807</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0004048228485579081</v>
+        <v>0.0008096456971158162</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0004074670059039744</v>
+        <v>0.0008149340118079488</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0004091460534274017</v>
+        <v>0.0008182921068548034</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0004099376412791659</v>
+        <v>0.0008198752825583318</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0004099145457893907</v>
+        <v>0.0008198290915787815</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0004091449442057913</v>
+        <v>0.0008182898884115826</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0004076926748518725</v>
+        <v>0.000815385349703745</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004056174834492777</v>
+        <v>0.0008112349668985554</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0004029752563116883</v>
+        <v>0.0008059505126233766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0003998182410824807</v>
+        <v>0.0007996364821649614</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000396195255654874</v>
+        <v>0.000792390511309748</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0003921518858814575</v>
+        <v>0.0007843037717629151</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000387730672649697</v>
+        <v>0.000775461345299394</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0003829712888712184</v>
+        <v>0.0007659425777424368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0003779107069052589</v>
+        <v>0.0007558214138105178</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0003725833569106297</v>
+        <v>0.0007451667138212594</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0003670212765957447</v>
+        <v>0.0007340425531914894</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.0003902439024390245</v>
+        <v>0.000780487804878049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0003963024778901831</v>
+        <v>0.0007926049557803662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0004011307673154035</v>
+        <v>0.000802261534630807</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0004048228485579081</v>
+        <v>0.0008096456971158162</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0004074670059039744</v>
+        <v>0.0008149340118079488</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004091460534274017</v>
+        <v>0.0008182921068548034</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0004099376412791659</v>
+        <v>0.0008198752825583318</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0004099145457893907</v>
+        <v>0.0008198290915787815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0004091449442057913</v>
+        <v>0.0008182898884115826</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0004076926748518725</v>
+        <v>0.000815385349703745</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0004056174834492777</v>
+        <v>0.0008112349668985554</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0004029752563116883</v>
+        <v>0.0008059505126233766</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0003998182410824807</v>
+        <v>0.0007996364821649614</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000396195255654874</v>
+        <v>0.000792390511309748</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0003921518858814575</v>
+        <v>0.0007843037717629151</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000387730672649697</v>
+        <v>0.000775461345299394</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0003829712888712184</v>
+        <v>0.0007659425777424368</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0003779107069052589</v>
+        <v>0.0007558214138105178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0003725833569106297</v>
+        <v>0.0007451667138212594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0003670212765957447</v>
+        <v>0.0007340425531914894</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/97.xlsx
+++ b/BVSimulationFiles/97.xlsx
@@ -483,64 +483,64 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.000780487804878049</v>
+        <v>0.00780487804878049</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007926049557803662</v>
+        <v>0.007926049557803662</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000802261534630807</v>
+        <v>0.008022615346308071</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008096456971158162</v>
+        <v>0.008096456971158163</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008149340118079488</v>
+        <v>0.008149340118079489</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008182921068548034</v>
+        <v>0.008182921068548035</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008198752825583318</v>
+        <v>0.008198752825583319</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008198290915787815</v>
+        <v>0.008198290915787814</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008182898884115826</v>
+        <v>0.008182898884115827</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000815385349703745</v>
+        <v>0.00815385349703745</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008112349668985554</v>
+        <v>0.008112349668985554</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0008059505126233766</v>
+        <v>0.008059505126233766</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0007996364821649614</v>
+        <v>0.007996364821649615</v>
       </c>
       <c r="O2" t="n">
-        <v>0.000792390511309748</v>
+        <v>0.007923905113097481</v>
       </c>
       <c r="P2" t="n">
-        <v>0.0007843037717629151</v>
+        <v>0.007843037717629151</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.000775461345299394</v>
+        <v>0.00775461345299394</v>
       </c>
       <c r="R2" t="n">
-        <v>0.0007659425777424368</v>
+        <v>0.007659425777424368</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0007558214138105178</v>
+        <v>0.007558214138105178</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0007451667138212594</v>
+        <v>0.007451667138212594</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0007340425531914894</v>
+        <v>0.007340425531914894</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +548,64 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.000780487804878049</v>
+        <v>0.00780487804878049</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007926049557803662</v>
+        <v>0.007926049557803662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000802261534630807</v>
+        <v>0.008022615346308071</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0008096456971158162</v>
+        <v>0.008096456971158163</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008149340118079488</v>
+        <v>0.008149340118079489</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008182921068548034</v>
+        <v>0.008182921068548035</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008198752825583318</v>
+        <v>0.008198752825583319</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008198290915787815</v>
+        <v>0.008198290915787814</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008182898884115826</v>
+        <v>0.008182898884115827</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000815385349703745</v>
+        <v>0.00815385349703745</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008112349668985554</v>
+        <v>0.008112349668985554</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0008059505126233766</v>
+        <v>0.008059505126233766</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0007996364821649614</v>
+        <v>0.007996364821649615</v>
       </c>
       <c r="O3" t="n">
-        <v>0.000792390511309748</v>
+        <v>0.007923905113097481</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0007843037717629151</v>
+        <v>0.007843037717629151</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.000775461345299394</v>
+        <v>0.00775461345299394</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0007659425777424368</v>
+        <v>0.007659425777424368</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0007558214138105178</v>
+        <v>0.007558214138105178</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0007451667138212594</v>
+        <v>0.007451667138212594</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0007340425531914894</v>
+        <v>0.007340425531914894</v>
       </c>
     </row>
   </sheetData>

--- a/BVSimulationFiles/97.xlsx
+++ b/BVSimulationFiles/97.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -421,61 +421,37 @@
         <v>0</v>
       </c>
       <c r="C1" t="n">
-        <v>0.03239315789473684</v>
+        <v>0.02122310344827586</v>
       </c>
       <c r="D1" t="n">
-        <v>0.06478631578947368</v>
+        <v>0.04244620689655172</v>
       </c>
       <c r="E1" t="n">
-        <v>0.09717947368421052</v>
+        <v>0.06366931034482759</v>
       </c>
       <c r="F1" t="n">
-        <v>0.1295726315789474</v>
+        <v>0.08489241379310344</v>
       </c>
       <c r="G1" t="n">
-        <v>0.1619657894736842</v>
+        <v>0.1061155172413793</v>
       </c>
       <c r="H1" t="n">
-        <v>0.194358947368421</v>
+        <v>0.1273386206896552</v>
       </c>
       <c r="I1" t="n">
-        <v>0.2267521052631579</v>
+        <v>0.148561724137931</v>
       </c>
       <c r="J1" t="n">
-        <v>0.2591452631578947</v>
+        <v>0.1697848275862069</v>
       </c>
       <c r="K1" t="n">
-        <v>0.2915384210526316</v>
+        <v>0.1910079310344827</v>
       </c>
       <c r="L1" t="n">
-        <v>0.3239315789473685</v>
+        <v>0.2122310344827586</v>
       </c>
       <c r="M1" t="n">
-        <v>0.3563247368421052</v>
-      </c>
-      <c r="N1" t="n">
-        <v>0.3887178947368421</v>
-      </c>
-      <c r="O1" t="n">
-        <v>0.4211110526315789</v>
-      </c>
-      <c r="P1" t="n">
-        <v>0.4535042105263157</v>
-      </c>
-      <c r="Q1" t="n">
-        <v>0.4858973684210526</v>
-      </c>
-      <c r="R1" t="n">
-        <v>0.5182905263157894</v>
-      </c>
-      <c r="S1" t="n">
-        <v>0.5506836842105263</v>
-      </c>
-      <c r="T1" t="n">
-        <v>0.5830768421052632</v>
-      </c>
-      <c r="U1" t="n">
-        <v>0.61547</v>
+        <v>0.2334541379310345</v>
       </c>
     </row>
     <row r="2">
@@ -483,64 +459,40 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.00780487804878049</v>
+        <v>0.05408151119104392</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007926049557803662</v>
+        <v>0.05644226666211404</v>
       </c>
       <c r="D2" t="n">
-        <v>0.008022615346308071</v>
+        <v>0.05837315054328313</v>
       </c>
       <c r="E2" t="n">
-        <v>0.008096456971158163</v>
+        <v>0.05991467607531686</v>
       </c>
       <c r="F2" t="n">
-        <v>0.008149340118079489</v>
+        <v>0.06110417978796672</v>
       </c>
       <c r="G2" t="n">
-        <v>0.008182921068548035</v>
+        <v>0.06197604953850773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.008198752825583319</v>
+        <v>0.06256193701111894</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008198290915787814</v>
+        <v>0.06289095570020277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.008182898884115827</v>
+        <v>0.06298986533500252</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00815385349703745</v>
+        <v>0.06288324364128881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.008112349668985554</v>
+        <v>0.06259364627818637</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008059505126233766</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.007996364821649615</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.007923905113097481</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.007843037717629151</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.00775461345299394</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.007659425777424368</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.007558214138105178</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.007451667138212594</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.007340425531914894</v>
+        <v>0.06214175573416012</v>
       </c>
     </row>
     <row r="3">
@@ -548,64 +500,40 @@
         <v>0.955</v>
       </c>
       <c r="B3" t="n">
-        <v>0.00780487804878049</v>
+        <v>0.05408151119104392</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007926049557803662</v>
+        <v>0.05644226666211404</v>
       </c>
       <c r="D3" t="n">
-        <v>0.008022615346308071</v>
+        <v>0.05837315054328313</v>
       </c>
       <c r="E3" t="n">
-        <v>0.008096456971158163</v>
+        <v>0.05991467607531686</v>
       </c>
       <c r="F3" t="n">
-        <v>0.008149340118079489</v>
+        <v>0.06110417978796672</v>
       </c>
       <c r="G3" t="n">
-        <v>0.008182921068548035</v>
+        <v>0.06197604953850773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.008198752825583319</v>
+        <v>0.06256193701111894</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008198290915787814</v>
+        <v>0.06289095570020277</v>
       </c>
       <c r="J3" t="n">
-        <v>0.008182898884115827</v>
+        <v>0.06298986533500252</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00815385349703745</v>
+        <v>0.06288324364128881</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008112349668985554</v>
+        <v>0.06259364627818637</v>
       </c>
       <c r="M3" t="n">
-        <v>0.008059505126233766</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0.007996364821649615</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0.007923905113097481</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0.007843037717629151</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>0.00775461345299394</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0.007659425777424368</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0.007558214138105178</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0.007451667138212594</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0.007340425531914894</v>
+        <v>0.06214175573416012</v>
       </c>
     </row>
   </sheetData>
